--- a/lancamento.xlsx
+++ b/lancamento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,21 +456,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3.01.01.03.0003</t>
+          <t>2.01.01.04.0002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>( - ) PIS/PASEP</t>
+          <t>PIS a Recolher</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>808.5</v>
+        <v>4414.39</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A100 - 107</t>
+          <t>A100 - 105</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -483,21 +483,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.01.01.04.0002</t>
+          <t>3.01.01.03.0003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PIS a Recolher</t>
+          <t>( - ) PIS/PASEP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>808.5</v>
+        <v>4414.39</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A100 - 107</t>
+          <t>A100 - 105</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -510,21 +510,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3.01.01.03.0004</t>
+          <t>2.01.01.04.0003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>( - ) COFINS</t>
+          <t>COFINS a Recolher</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3724</v>
+        <v>20332.97</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>A100 - 107</t>
+          <t>A100 - 105</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -537,21 +537,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.01.01.04.0003</t>
+          <t>3.01.01.03.0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COFINS a Recolher</t>
+          <t>( - ) COFINS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>3724</v>
+        <v>20332.97</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>A100 - 107</t>
+          <t>A100 - 105</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -564,21 +564,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1.01.05.01.0003</t>
+          <t>3.01.01.03.0003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PIS a Recuperar</t>
+          <t>( - ) PIS/PASEP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31.76</v>
+        <v>37.87</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C100 - 30407</t>
+          <t>A100 - 106</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -591,21 +591,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.01.01.03.0003</t>
+          <t>2.01.01.04.0002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>( - ) PIS/PASEP</t>
+          <t>PIS a Recolher</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>31.76</v>
+        <v>37.87</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C100 - 30407</t>
+          <t>A100 - 106</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -618,21 +618,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.01.05.01.0004</t>
+          <t>3.01.01.03.0004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COFINS a Recuperar</t>
+          <t>( - ) COFINS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.17999999999998</v>
+        <v>174.27</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C100 - 30407</t>
+          <t>A100 - 106</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -645,21 +645,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3.01.01.03.0004</t>
+          <t>2.01.01.04.0003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>( - ) COFINS</t>
+          <t>COFINS a Recolher</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>16.17999999999998</v>
+        <v>174.27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C100 - 30407</t>
+          <t>A100 - 106</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -681,18 +681,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>201.71</v>
+        <v>789</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C100 - 18</t>
+          <t>A100 - 107</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
@@ -709,17 +709,17 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>201.71</v>
+        <v>789</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C100 - 18</t>
+          <t>A100 - 107</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
@@ -735,18 +735,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>93.4799999999999</v>
+        <v>3634</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C100 - 18</t>
+          <t>A100 - 107</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
@@ -763,155 +763,149 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>93.4799999999999</v>
+        <v>3634</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C100 - 18</t>
+          <t>A100 - 107</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3.01.01.03.0003</t>
+          <t>2.01.01.04.0002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>( - ) PIS/PASEP</t>
+          <t>PIS a Recolher</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34.79</v>
+        <v>300.07</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C100 - 39</t>
+          <t>A100 - 108</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2.01.01.04.0002</t>
+          <t>3.01.01.03.0003</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PIS a Recolher</t>
+          <t>( - ) PIS/PASEP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>34.79</v>
+        <v>300.07</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C100 - 39</t>
+          <t>A100 - 108</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3.01.01.03.0004</t>
+          <t>2.01.01.04.0003</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>( - ) COFINS</t>
+          <t>COFINS a Recolher</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>160.24</v>
+        <v>1382.14</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C100 - 39</t>
+          <t>A100 - 108</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2.01.01.04.0003</t>
+          <t>3.01.01.03.0004</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COFINS a Recolher</t>
+          <t>( - ) COFINS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>160.24</v>
+        <v>1382.14</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C100 - 39</t>
+          <t>A100 - 108</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>04784935001210</t>
+          <t>04784935000167</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4.01.01.01.0001</t>
+          <t>3.01.01.03.0003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Custo dos Produtos Vendidos</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3359,77</t>
-        </is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>18723.14</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>M110</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 109</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -921,30 +915,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.01.05.01.0003</t>
+          <t>2.01.01.04.0002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PIS a Recuperar</t>
+          <t>PIS a Recolher</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3359,77</t>
-        </is>
+      <c r="D19" t="n">
+        <v>18723.14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M110</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 109</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -954,28 +942,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2.01.01.04.0002</t>
+          <t>3.01.01.03.0004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PIS a Recolher</t>
+          <t>( - ) COFINS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3526.31565</v>
+        <v>86239.89999999999</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>M215</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 109</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -985,28 +969,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.01.05.01.0003</t>
+          <t>2.01.01.04.0003</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PIS a Recuperar</t>
+          <t>COFINS a Recolher</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>3526.31565</v>
+        <v>86239.89999999999</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>M215</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 109</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -1016,30 +996,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4.01.01.01.0001</t>
+          <t>2.01.01.04.0002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Custo dos Produtos Vendidos</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>15475,3</t>
-        </is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>833.1900000000001</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>M510</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 110</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -1049,30 +1023,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.01.05.01.0004</t>
+          <t>3.01.01.03.0003</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COFINS a Recuperar</t>
+          <t>( - ) PIS/PASEP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>15475,3</t>
-        </is>
+      <c r="D23" t="n">
+        <v>833.1900000000001</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M510</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 110</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -1091,19 +1059,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16242.4236</v>
+        <v>3837.72</v>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>M615</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>OBRAS</t>
-        </is>
-      </c>
+          <t>A100 - 110</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>04784935000167</t>
@@ -1113,29 +1077,929 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1.01.05.01.0004</t>
+          <t>3.01.01.03.0004</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COFINS a Recuperar</t>
+          <t>( - ) COFINS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
+        <v>3837.72</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>A100 - 110</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0002</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3661.12</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>A100 - 111</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0003</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>3661.12</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>A100 - 111</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0003</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>COFINS a Recolher</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16907</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>A100 - 111</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0004</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>( - ) COFINS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>16907</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>A100 - 111</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0003</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1879.07</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>A100 - 112</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0002</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>1879.07</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>A100 - 112</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0004</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>( - ) COFINS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8655.07</v>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>A100 - 112</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0003</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>COFINS a Recolher</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>8655.07</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>A100 - 112</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>A100 - 113</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0003</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>A100 - 113</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0003</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>COFINS a Recolher</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>222.39</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>A100 - 113</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0004</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>( - ) COFINS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>222.39</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>A100 - 113</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1.01.05.01.0003</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PIS a Recuperar</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>C100 - 30407</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0003</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>C100 - 30407</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1.01.05.01.0004</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>COFINS a Recuperar</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.17999999999998</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>C100 - 30407</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0004</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>( - ) COFINS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>16.17999999999998</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>C100 - 30407</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0003</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>201.71</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>C100 - 18</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>201.71</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>C100 - 18</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0004</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>( - ) COFINS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>93.4799999999999</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>C100 - 18</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0003</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>COFINS a Recolher</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>93.4799999999999</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>C100 - 18</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0003</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>( - ) PIS/PASEP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>C100 - 39</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>C100 - 39</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3.01.01.03.0004</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>( - ) COFINS</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>160.24</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>C100 - 39</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0003</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>COFINS a Recolher</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>160.24</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>C100 - 39</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>04784935001210</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4.01.01.01.0001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Custo dos Produtos Vendidos</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3359,77</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>M110</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1.01.05.01.0003</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PIS a Recuperar</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3359,77</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>M110</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PIS a Recolher</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3526.31565</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>M215</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1.01.05.01.0003</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PIS a Recuperar</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>3526.31565</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>M215</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4.01.01.01.0001</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Custo dos Produtos Vendidos</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>15475,3</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>M510</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1.01.05.01.0004</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>COFINS a Recuperar</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>15475,3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>M510</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2.01.01.04.0003</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>COFINS a Recolher</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
         <v>16242.4236</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
         <is>
           <t>M615</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>OBRAS</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>04784935000167</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1.01.05.01.0004</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>COFINS a Recuperar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>16242.4236</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>M615</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OBRAS</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>04784935000167</t>
         </is>
